--- a/TASTI_SYNTHETIC/PnoTMO.xlsx
+++ b/TASTI_SYNTHETIC/PnoTMO.xlsx
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>89L218K963</t>
+          <t>85P440L610</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TMO-FUL-83L</t>
+          <t>TMO-SEM-07L</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -454,23 +454,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MINERAL</t>
+          <t>SEMI SYNTHETIC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>38B790F133</t>
+          <t>37N358Y580</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TMO-SEM-29L</t>
+          <t>TMO-FUL-81L</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -481,12 +481,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>71J223B266</t>
+          <t>43K359P654</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TMO-MIN-77L</t>
+          <t>TMO-MIN-85L</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -494,19 +494,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FULL SYNTHETIC</t>
+          <t>SEMI SYNTHETIC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23A433V455</t>
+          <t>84N838B423</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TMO-SEM-01L</t>
+          <t>TMO-SEM-83L</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -521,32 +521,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13X668Z623</t>
+          <t>44T632M601</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TMO-MIN-18L</t>
+          <t>TMO-FUL-13L</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SEMI SYNTHETIC</t>
+          <t>FULL SYNTHETIC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>52N105K497</t>
+          <t>70Z186V901</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TMO-SEM-91L</t>
+          <t>TMO-FUL-46L</t>
         </is>
       </c>
       <c r="C7" t="n">
